--- a/public/templates/operations_template.xlsx
+++ b/public/templates/operations_template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Template" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -401,7 +401,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>internalCode</v>
+        <v>_id</v>
       </c>
       <c r="B1" t="str">
         <v>name</v>
@@ -415,7 +415,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>TEMP_CHECK</v>
+        <v/>
       </c>
       <c r="B2" t="str">
         <v>Temperature Check</v>
@@ -429,7 +429,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>PRESSURE_READ</v>
+        <v/>
       </c>
       <c r="B3" t="str">
         <v>Pressure Reading</v>
@@ -443,7 +443,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>VISUAL_INSP</v>
+        <v/>
       </c>
       <c r="B4" t="str">
         <v>Visual Inspection</v>
@@ -457,7 +457,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>MAINT_DATE</v>
+        <v/>
       </c>
       <c r="B5" t="str">
         <v>Maintenance Date</v>
@@ -471,7 +471,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>START_TIME</v>
+        <v/>
       </c>
       <c r="B6" t="str">
         <v>Start Time</v>
@@ -485,7 +485,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>COMPLETION</v>
+        <v/>
       </c>
       <c r="B7" t="str">
         <v>Completion Status</v>
@@ -499,7 +499,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>NOTES</v>
+        <v/>
       </c>
       <c r="B8" t="str">
         <v>Notes</v>

--- a/public/templates/operations_template.xlsx
+++ b/public/templates/operations_template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Template" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -401,7 +401,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>_id</v>
+        <v>internalCode</v>
       </c>
       <c r="B1" t="str">
         <v>name</v>
@@ -415,7 +415,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v/>
+        <v>TEMP_CHECK</v>
       </c>
       <c r="B2" t="str">
         <v>Temperature Check</v>
@@ -429,7 +429,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v/>
+        <v>PRESSURE_READ</v>
       </c>
       <c r="B3" t="str">
         <v>Pressure Reading</v>
@@ -443,7 +443,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v/>
+        <v>VISUAL_INSP</v>
       </c>
       <c r="B4" t="str">
         <v>Visual Inspection</v>
@@ -457,7 +457,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v/>
+        <v>MAINT_DATE</v>
       </c>
       <c r="B5" t="str">
         <v>Maintenance Date</v>
@@ -471,7 +471,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v/>
+        <v>START_TIME</v>
       </c>
       <c r="B6" t="str">
         <v>Start Time</v>
@@ -485,7 +485,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v/>
+        <v>COMPLETION</v>
       </c>
       <c r="B7" t="str">
         <v>Completion Status</v>
@@ -499,7 +499,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v/>
+        <v>NOTES</v>
       </c>
       <c r="B8" t="str">
         <v>Notes</v>
